--- a/howTo26/How to Succeed cast list.xlsx
+++ b/howTo26/How to Succeed cast list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Seagate X/RVCOprod/website/howTo26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC52930-6DF7-B841-9791-AA6564F2AD25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BC7D6B-263E-2945-8C56-F6E6D37B025C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="600" windowWidth="28980" windowHeight="21000" xr2:uid="{E38B6315-D279-724B-88A4-0AE2C1BF2347}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$G$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$G$30</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="106">
   <si>
     <t xml:space="preserve">EMERGENCY CONTACT </t>
   </si>
@@ -297,12 +297,6 @@
   </si>
   <si>
     <t>Grace Albert</t>
-  </si>
-  <si>
-    <t>Laura Hull</t>
-  </si>
-  <si>
-    <t>lmarkow07@gmail.com</t>
   </si>
   <si>
     <t>Bill</t>
@@ -895,7 +889,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -925,16 +919,16 @@
         <v>0</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="18"/>
@@ -1015,7 +1009,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H5" s="7">
         <v>3</v>
@@ -1201,10 +1195,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C13" s="18">
         <v>6107317668</v>
@@ -1215,7 +1209,7 @@
       </c>
       <c r="F13" s="17"/>
       <c r="G13" s="17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H13" s="7">
         <v>11</v>
@@ -1284,7 +1278,7 @@
         <v>6106629204</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E16" s="23">
         <v>3034948820</v>
@@ -1293,7 +1287,7 @@
         <v>3</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H16" s="11">
         <v>14</v>
@@ -1319,7 +1313,7 @@
         <v>3</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H17" s="7">
         <v>14</v>
@@ -1371,7 +1365,7 @@
         <v>3</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H19" s="7">
         <v>17</v>
@@ -1385,7 +1379,7 @@
         <v>22</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>23</v>
@@ -1397,7 +1391,7 @@
         <v>3</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H20" s="7">
         <v>18</v>
@@ -1423,7 +1417,7 @@
         <v>3</v>
       </c>
       <c r="G21" s="28" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H21" s="7">
         <v>19</v>
@@ -1449,49 +1443,53 @@
         <v>3</v>
       </c>
       <c r="G22" s="28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H22" s="7">
         <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
-        <v>87</v>
+      <c r="A23" s="25" t="s">
+        <v>61</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="23">
-        <v>6106270433</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="C23" s="22">
+        <v>6102914298</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="29"/>
       <c r="F23" s="24"/>
       <c r="G23" s="25" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H23" s="7">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="25" t="s">
-        <v>61</v>
+    <row r="24" spans="1:8" ht="26" x14ac:dyDescent="0.2">
+      <c r="A24" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="C24" s="22">
-        <v>6102914298</v>
-      </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="25" t="s">
-        <v>107</v>
+        <v>2158963528</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="23">
+        <v>6107169026</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>104</v>
       </c>
       <c r="H24" s="7">
         <v>22</v>
@@ -1499,130 +1497,113 @@
     </row>
     <row r="25" spans="1:8" ht="26" x14ac:dyDescent="0.2">
       <c r="A25" s="20" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="C25" s="22">
-        <v>2158963528</v>
+        <v>4844375278</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="E25" s="23">
-        <v>6107169026</v>
+        <v>6107048442</v>
       </c>
       <c r="F25" s="24" t="s">
         <v>3</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H25" s="7">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="26" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="22">
-        <v>4844375278</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="23">
-        <v>6107048442</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="G26" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="H26" s="7">
-        <v>25</v>
-      </c>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="20"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="25"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="24"/>
+      <c r="A27" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="25"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="33"/>
       <c r="G27" s="25"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="B28" s="25"/>
-      <c r="C28" s="31"/>
+      <c r="A28" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="31">
+        <v>2158406582</v>
+      </c>
       <c r="D28" s="25"/>
       <c r="E28" s="31"/>
       <c r="F28" s="33"/>
-      <c r="G28" s="25"/>
-    </row>
-    <row r="29" spans="1:8" ht="26" x14ac:dyDescent="0.2">
+      <c r="G28" s="25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" s="36" t="s">
-        <v>81</v>
+        <v>84</v>
+      </c>
+      <c r="B29" s="37" t="s">
+        <v>85</v>
       </c>
       <c r="C29" s="31">
-        <v>2158406582</v>
+        <v>2679344650</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="31"/>
       <c r="F29" s="33"/>
       <c r="G29" s="25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="25" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C30" s="31">
-        <v>2679344650</v>
-      </c>
-      <c r="D30" s="25"/>
-      <c r="E30" s="31"/>
+        <v>6105470348</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="E30" s="31">
+        <v>61030809876</v>
+      </c>
       <c r="F30" s="33"/>
       <c r="G30" s="25" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="B31" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" s="31">
-        <v>6105470348</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="31">
-        <v>61030809876</v>
-      </c>
-      <c r="F31" s="33"/>
-      <c r="G31" s="25" t="s">
-        <v>89</v>
-      </c>
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="4"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
@@ -1665,7 +1646,7 @@
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="5"/>
+      <c r="E36" s="4"/>
       <c r="F36" s="6"/>
       <c r="G36" s="4"/>
     </row>
@@ -1681,7 +1662,7 @@
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
-      <c r="C38" s="5"/>
+      <c r="C38" s="6"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="6"/>
@@ -1697,28 +1678,19 @@
       <c r="G39" s="4"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="4"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="8"/>
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="8"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A20:H26">
-    <sortCondition ref="H20:H26"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A20:H25">
+    <sortCondition ref="H20:H25"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="89" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup scale="93" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>